--- a/assets/docs/lop5/Toan - Lop 5.xlsx
+++ b/assets/docs/lop5/Toan - Lop 5.xlsx
@@ -1675,12 +1675,12 @@
       <c r="D41" s="4" t="inlineStr"/>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>Bài 18. Luyện tập chung (Tiết 1)</t>
+          <t>Bài 18. Luyện tập chung</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>2 tiết</t>
+          <t>1 tiết</t>
         </is>
       </c>
       <c r="G41" s="4" t="inlineStr">
@@ -1690,7 +1690,8 @@
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 5 (Cơ bản, bậc 2): Ở tiết luyện tập chung, GV cho HS làm bộ câu hỏi tương tác có chấm tự động về số thập phân và các phép tính đã học
+          <t>SGV 2 tiết; bớt 1 tiết cho kiểm tra định kì
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở tiết luyện tập chung, GV cho HS làm bộ câu hỏi tương tác có chấm tự động về số thập phân và các phép tính đã học
 Năng lực số Miền 1 (Cơ bản, bậc 2): GV chiếu bài toán thực tế có bảng số liệu, tô màu dòng và cột cần dùng theo lời HS đọc đề; các em học cách đọc bảng</t>
         </is>
       </c>
@@ -1703,27 +1704,27 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 3: Một số đơn vị đo diện tích</t>
+          <t>Ôn tập, kiểm tra, đánh giá</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr"/>
       <c r="D42" s="4" t="inlineStr"/>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>Bài 18. Luyện tập chung (Tiết 2)</t>
-        </is>
-      </c>
-      <c r="F42" s="4" t="inlineStr"/>
+          <t>Kiểm tra định kì giữa học kì I</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
           <t>39</t>
         </is>
       </c>
-      <c r="H42" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 5.2 CB2b: HS quan sát tia số phóng to, thao tác trên bảng tính để thấy cách hiển thị và làm tròn số thập phân.</t>
-        </is>
-      </c>
+      <c r="H42" s="4" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
@@ -1755,7 +1756,7 @@
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 5.2 CB2b: HS quan sát tia số phóng to, thao tác trên bảng tính để thấy cách hiển thị và làm tròn số thập phân.</t>
+          <t>Năng lực số 5.2 CB2b: HS tự đặt tính, tính phép cộng số thập phân rồi dùng máy tính cầm tay hoặc bảng tính GV chiếu để đối chiếu kết quả.</t>
         </is>
       </c>
     </row>
@@ -1785,7 +1786,7 @@
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 5.2 CB2b: HS quan sát tia số phóng to, thao tác trên bảng tính để thấy cách hiển thị và làm tròn số thập phân.</t>
+          <t>Năng lực số 5.2 CB2b: HS tự đặt tính, tính phép cộng số thập phân rồi dùng máy tính cầm tay hoặc bảng tính GV chiếu để đối chiếu kết quả.</t>
         </is>
       </c>
     </row>
@@ -1861,19 +1862,19 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Ôn tập, kiểm tra, đánh giá</t>
+          <t>Chủ đề 4: Các phép tính với số thập phân</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr"/>
       <c r="D47" s="4" t="inlineStr"/>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>Kiểm tra định kì giữa học kì I</t>
+          <t>Bài 21. Phép nhân số thập phân (Tiết 1)</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>1 tiết</t>
+          <t>3 tiết</t>
         </is>
       </c>
       <c r="G47" s="4" t="inlineStr">
@@ -1881,7 +1882,11 @@
           <t>44</t>
         </is>
       </c>
-      <c r="H47" s="4" t="inlineStr"/>
+      <c r="H47" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số 5.2 CB2b: HS quan sát tia số phóng to, thao tác trên bảng tính để thấy cách hiển thị và làm tròn số thập phân.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
@@ -1898,14 +1903,10 @@
       <c r="D48" s="4" t="inlineStr"/>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>Bài 21. Phép nhân số thập phân (Tiết 1)</t>
-        </is>
-      </c>
-      <c r="F48" s="4" t="inlineStr">
-        <is>
-          <t>3 tiết</t>
-        </is>
-      </c>
+          <t>Bài 21. Phép nhân số thập phân (Tiết 2)</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="inlineStr"/>
       <c r="G48" s="4" t="inlineStr">
         <is>
           <t>45</t>
@@ -1932,7 +1933,7 @@
       <c r="D49" s="4" t="inlineStr"/>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>Bài 21. Phép nhân số thập phân (Tiết 2)</t>
+          <t>Bài 21. Phép nhân số thập phân (Tiết 3)</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr"/>
@@ -1941,11 +1942,7 @@
           <t>46</t>
         </is>
       </c>
-      <c r="H49" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 5.2 CB2b: HS quan sát tia số phóng to, thao tác trên bảng tính để thấy cách hiển thị và làm tròn số thập phân.</t>
-        </is>
-      </c>
+      <c r="H49" s="4" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
@@ -1962,16 +1959,24 @@
       <c r="D50" s="4" t="inlineStr"/>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>Bài 21. Phép nhân số thập phân (Tiết 3)</t>
-        </is>
-      </c>
-      <c r="F50" s="4" t="inlineStr"/>
+          <t>Bài 22. Phép chia số thập phân (Tiết 1)</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>4 tiết</t>
+        </is>
+      </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
           <t>47</t>
         </is>
       </c>
-      <c r="H50" s="4" t="inlineStr"/>
+      <c r="H50" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số 5.2 CB2b: HS quan sát tia số phóng to, thao tác trên bảng tính để thấy cách hiển thị và làm tròn số thập phân.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
@@ -1988,14 +1993,10 @@
       <c r="D51" s="4" t="inlineStr"/>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>Bài 22. Phép chia số thập phân (Tiết 1)</t>
-        </is>
-      </c>
-      <c r="F51" s="4" t="inlineStr">
-        <is>
-          <t>4 tiết</t>
-        </is>
-      </c>
+          <t>Bài 22. Phép chia số thập phân (Tiết 2)</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr"/>
       <c r="G51" s="4" t="inlineStr">
         <is>
           <t>48</t>
@@ -2022,7 +2023,7 @@
       <c r="D52" s="4" t="inlineStr"/>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>Bài 22. Phép chia số thập phân (Tiết 2)</t>
+          <t>Bài 22. Phép chia số thập phân (Tiết 3)</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr"/>
@@ -2052,7 +2053,7 @@
       <c r="D53" s="4" t="inlineStr"/>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>Bài 22. Phép chia số thập phân (Tiết 3)</t>
+          <t>Bài 22. Phép chia số thập phân (Tiết 4)</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr"/>
@@ -2082,10 +2083,14 @@
       <c r="D54" s="4" t="inlineStr"/>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>Bài 22. Phép chia số thập phân (Tiết 4)</t>
-        </is>
-      </c>
-      <c r="F54" s="4" t="inlineStr"/>
+          <t>Bài 23. Nhân, chia số thập phân với 10; 100; 1 000;… hoặc với 0,1; 0,01; 0,001;… (Tiết 1)</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>2 tiết</t>
+        </is>
+      </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
           <t>51</t>
@@ -2112,14 +2117,10 @@
       <c r="D55" s="4" t="inlineStr"/>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>Bài 23. Nhân, chia số thập phân với 10; 100; 1 000;… hoặc với 0,1; 0,01; 0,001;… (Tiết 1)</t>
-        </is>
-      </c>
-      <c r="F55" s="4" t="inlineStr">
-        <is>
-          <t>2 tiết</t>
-        </is>
-      </c>
+          <t>Bài 23. Nhân, chia số thập phân với 10; 100; 1 000;… hoặc với 0,1; 0,01; 0,001;… (Tiết 2)</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="inlineStr"/>
       <c r="G55" s="4" t="inlineStr">
         <is>
           <t>52</t>
@@ -2146,10 +2147,14 @@
       <c r="D56" s="4" t="inlineStr"/>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>Bài 23. Nhân, chia số thập phân với 10; 100; 1 000;… hoặc với 0,1; 0,01; 0,001;… (Tiết 2)</t>
-        </is>
-      </c>
-      <c r="F56" s="4" t="inlineStr"/>
+          <t>Bài 24. Luyện tập chung (Tiết 1)</t>
+        </is>
+      </c>
+      <c r="F56" s="4" t="inlineStr">
+        <is>
+          <t>3 tiết</t>
+        </is>
+      </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
           <t>53</t>
@@ -2157,7 +2162,8 @@
       </c>
       <c r="H56" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 5.2 CB2b: HS quan sát tia số phóng to, thao tác trên bảng tính để thấy cách hiển thị và làm tròn số thập phân.</t>
+          <t>Năng lực số Miền 5 (Cơ bản, bậc 2): Ở tiết luyện tập chung, GV cho HS làm bộ câu hỏi tương tác có chấm tự động; sau mỗi câu các em biết ngay đúng hay sai
+Năng lực số Miền 1 (Cơ bản, bậc 2): GV chiếu bài toán thực tế có bảng số liệu, tô màu dòng và cột cần dùng theo lời HS đọc đề; các em học cách đọc bảng</t>
         </is>
       </c>
     </row>
@@ -2176,26 +2182,16 @@
       <c r="D57" s="4" t="inlineStr"/>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>Bài 24. Luyện tập chung (Tiết 1)</t>
-        </is>
-      </c>
-      <c r="F57" s="4" t="inlineStr">
-        <is>
-          <t>2 tiết</t>
-        </is>
-      </c>
+          <t>Bài 24. Luyện tập chung (Tiết 2)</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="inlineStr"/>
       <c r="G57" s="4" t="inlineStr">
         <is>
           <t>54</t>
         </is>
       </c>
-      <c r="H57" s="4" t="inlineStr">
-        <is>
-          <t>SGV 3 tiết; bớt 1 tiết cho kiểm tra định kì
-Năng lực số Miền 5 (Cơ bản, bậc 2): Ở tiết luyện tập chung, GV cho HS làm bộ câu hỏi tương tác có chấm tự động; sau mỗi câu các em biết ngay đúng hay sai
-Năng lực số Miền 1 (Cơ bản, bậc 2): GV chiếu bài toán thực tế có bảng số liệu, tô màu dòng và cột cần dùng theo lời HS đọc đề; các em học cách đọc bảng</t>
-        </is>
-      </c>
+      <c r="H57" s="4" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
@@ -2212,7 +2208,7 @@
       <c r="D58" s="4" t="inlineStr"/>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>Bài 24. Luyện tập chung (Tiết 2)</t>
+          <t>Bài 24. Luyện tập chung (Tiết 3)</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr"/>
